--- a/reports/оприходование-офис-2026-08-31.xlsx
+++ b/reports/оприходование-офис-2026-08-31.xlsx
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2066-06-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>вторая партия «2 - 06/66»: год 66 явно описка</t>
+          <t>срок на листе «06/66» прочитан как 06/26 — исправлено по решению оператора; вторая партия «2 - 06/66»: год 66 явно описка</t>
         </is>
       </c>
     </row>

--- a/reports/оприходование-офис-2026-08-31.xlsx
+++ b/reports/оприходование-офис-2026-08-31.xlsx
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Фарфоровый</t>
+          <t>Увлажняющая тональная основа the one aqua boost - фарфоровый</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Фарфоровый</t>
+          <t>Увлажняющая тональная основа the one aqua boost - фарфоровый</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Фарфоровый</t>
+          <t>Увлажняющая тональная основа the one aqua boost - фарфоровый</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Розовый нюд</t>
+          <t>Увлажняющая тональная основа the one aqua boost - розовый нюд</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Слоновая кость</t>
+          <t>Увлажняющая тональная основа the one aqua boost - слоновая кость</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Естественный беж</t>
+          <t>Увлажняющая тональная основа the one aqua boost - естественный беж</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Естественный беж</t>
+          <t>Увлажняющая тональная основа the one aqua boost - естественный беж</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Слоновая кость</t>
+          <t>Ультрастойкая корректирующая тональная основа spf 30 the one everlasting - слоновая кость</t>
         </is>
       </c>
       <c r="D394" t="n">
